--- a/问题四/output/问题4-2_指定日期结果.xlsx
+++ b/问题四/output/问题4-2_指定日期结果.xlsx
@@ -613,7 +613,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>69691.38024403834</v>
+        <v>69691.38024403836</v>
       </c>
     </row>
   </sheetData>

--- a/问题四/output/问题4-2_指定日期结果.xlsx
+++ b/问题四/output/问题4-2_指定日期结果.xlsx
@@ -499,25 +499,25 @@
         <v>55439.41991666666</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>66316.8114583498</v>
+        <v>72942.0362627397</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>21620.26127201646</v>
+        <v>21731.47810006481</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>17512.41163033333</v>
+        <v>17556.36337908333</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>0</v>
+        <v>402.0538900833399</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>40587.35712485121</v>
+        <v>45631.24728427501</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0</v>
+        <v>2084.543860326368</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>40587.35712485121</v>
+        <v>47715.79114460137</v>
       </c>
     </row>
     <row r="3">
@@ -531,25 +531,25 @@
         <v>62073.3244</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>33229.13910884774</v>
+        <v>36037.35884483084</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>18956.73329218107</v>
+        <v>17098.23680860288</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>15354.95396666667</v>
+        <v>13376.85565825249</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>15478.71530669584</v>
+        <v>19233.91543714997</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0</v>
+        <v>1.184901066153543e-13</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>15478.71530669584</v>
+        <v>19233.91543714997</v>
       </c>
     </row>
     <row r="4">
@@ -563,25 +563,25 @@
         <v>59065.66575</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>66265.42130905349</v>
+        <v>68276.81518487277</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>21835.81960905349</v>
+        <v>18145.78788101851</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>17687.01388333333</v>
+        <v>16321.60975502778</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0</v>
+        <v>6.375000000000114</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>42728.75851619014</v>
+        <v>46262.0857404733</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0</v>
+        <v>44.07993750000047</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>42728.75851619014</v>
+        <v>46306.16567797329</v>
       </c>
     </row>
     <row r="5">
@@ -595,25 +595,25 @@
         <v>35338.6591</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>93770.21493971194</v>
+        <v>92691.37131000659</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>24907.54248971193</v>
+        <v>21831.00154168507</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>20175.10941666667</v>
+        <v>17954.1729446785</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0</v>
+        <v>391.4820369999948</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>69691.38024403834</v>
+        <v>71584.72142382459</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0</v>
+        <v>3056.691744895959</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>69691.38024403836</v>
+        <v>74641.41316872055</v>
       </c>
     </row>
   </sheetData>

--- a/问题四/output/问题4-2_指定日期结果.xlsx
+++ b/问题四/output/问题4-2_指定日期结果.xlsx
@@ -499,25 +499,25 @@
         <v>55439.41991666666</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>72942.0362627397</v>
+        <v>62089.91623638064</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>21731.47810006481</v>
+        <v>17906.0763729991</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>17556.36337908333</v>
+        <v>14410.69498222828</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>402.0538900833399</v>
+        <v>3649.041875140923</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>45631.24728427501</v>
+        <v>39028.68805294739</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>2084.543860326368</v>
+        <v>21444.39402389689</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>47715.79114460137</v>
+        <v>60473.08207684428</v>
       </c>
     </row>
     <row r="3">
@@ -531,25 +531,25 @@
         <v>62073.3244</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>36037.35884483084</v>
+        <v>34120.55166182398</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>17098.23680860288</v>
+        <v>13546.41837179527</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>13376.85565825249</v>
+        <v>10589.83192590917</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>172.6704773190164</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>19233.91543714997</v>
+        <v>17268.6107316147</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1.184901066153543e-13</v>
+        <v>510.5842514386967</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>19233.91543714997</v>
+        <v>17779.1949830534</v>
       </c>
     </row>
     <row r="4">
@@ -563,25 +563,25 @@
         <v>59065.66575</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>68276.81518487277</v>
+        <v>65407.62671049626</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>18145.78788101851</v>
+        <v>19348.43546879602</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>16321.60975502778</v>
+        <v>16073.95191768423</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>6.375000000000114</v>
+        <v>539.7345078629594</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46262.0857404733</v>
+        <v>43714.75473215225</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>44.07993750000047</v>
+        <v>3542.010079863494</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>46306.16567797329</v>
+        <v>47256.76481201575</v>
       </c>
     </row>
     <row r="5">
@@ -595,25 +595,25 @@
         <v>35338.6591</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>92691.37131000659</v>
+        <v>96350.09431121967</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>21831.00154168507</v>
+        <v>23919.73222464349</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>17954.1729446785</v>
+        <v>19016.46144501391</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>391.4820369999948</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>71584.72142382459</v>
+        <v>73296.12167669171</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>3056.691744895959</v>
+        <v>0</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>74641.41316872055</v>
+        <v>73296.12167669171</v>
       </c>
     </row>
   </sheetData>
